--- a/police_officer_forms/007_use_of_force_authorization_form--police_officer_forms.xlsx
+++ b/police_officer_forms/007_use_of_force_authorization_form--police_officer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>suspect_name_1</t>
+          <t>suspect name 1</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>suspect_name_2</t>
+          <t>suspect name 2</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>suspect_name_3</t>
+          <t>suspect name 3</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>force_level_1</t>
+          <t>force level 1</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>force_level_2</t>
+          <t>force level 2</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>force_level_3</t>
+          <t>force level 3</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>witness_1</t>
+          <t>witness 1</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>witness_2</t>
+          <t>witness 2</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>witness_3</t>
+          <t>witness 3</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>witness_alt_1</t>
+          <t>witness alt 1</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>witness_alt_2</t>
+          <t>witness alt 2</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>witness_alt_3</t>
+          <t>witness alt 3</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>vehicle_1</t>
+          <t>vehicle 1</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>vehicle_2</t>
+          <t>vehicle 2</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>vehicle_3</t>
+          <t>vehicle 3</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>suspect_vehicle_1</t>
+          <t>suspect vehicle 1</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>suspect_vehicle_2</t>
+          <t>suspect vehicle 2</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>suspect_vehicle_3</t>
+          <t>suspect vehicle 3</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>officer_1</t>
+          <t>officer 1</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>officer_2</t>
+          <t>officer 2</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>officer_3</t>
+          <t>officer 3</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>weapons_used_1</t>
+          <t>weapons used 1</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>weapons_used_2</t>
+          <t>weapons used 2</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>weapons_used_3</t>
+          <t>weapons used 3</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>officer_alt_1</t>
+          <t>officer alt 1</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>officer_alt_2</t>
+          <t>officer alt 2</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>officer_alt_3</t>
+          <t>officer alt 3</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>suspect_injuries_1</t>
+          <t>suspect injuries 1</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>suspect_injuries_2</t>
+          <t>suspect injuries 2</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>suspect_injuries_3</t>
+          <t>suspect injuries 3</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>officer_injuries_1</t>
+          <t>officer injuries 1</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>officer_injuries_2</t>
+          <t>officer injuries 2</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>officer_injuries_3</t>
+          <t>officer injuries 3</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>other_involves_1</t>
+          <t>other involves 1</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>other_involves_2</t>
+          <t>other involves 2</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>other_involves_3</t>
+          <t>other involves 3</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>suspect_resistances_1</t>
+          <t>suspect resistances 1</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>suspect_resistances_2</t>
+          <t>suspect resistances 2</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>suspect_resistances_3</t>
+          <t>suspect resistances 3</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>suspect_alt_resistances_1</t>
+          <t>suspect alt resistances 1</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>suspect_alt_resistances_2</t>
+          <t>suspect alt resistances 2</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>suspect_alt_resistances_3</t>
+          <t>suspect alt resistances 3</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>officer_resistances_1</t>
+          <t>officer resistances 1</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>officer_resistances_2</t>
+          <t>officer resistances 2</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>officer_resistances_3</t>
+          <t>officer resistances 3</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>suspect_alt_resistances_1</t>
+          <t>suspect alt resistances 1</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>suspect_alt_resistances_2</t>
+          <t>suspect alt resistances 2</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>suspect_alt_resistances_3</t>
+          <t>suspect alt resistances 3</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>officer_alt_resistances_1</t>
+          <t>officer alt resistances 1</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>officer_alt_resistances_2</t>
+          <t>officer alt resistances 2</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>officer_alt_resistances_3</t>
+          <t>officer alt resistances 3</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>suspect_involves_1</t>
+          <t>suspect involves 1</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>suspect_involves_2</t>
+          <t>suspect involves 2</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>suspect_involves_3</t>
+          <t>suspect involves 3</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>suspect_alt_involves_1</t>
+          <t>suspect alt involves 1</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>suspect_alt_involves_2</t>
+          <t>suspect alt involves 2</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>suspect_alt_involves_3</t>
+          <t>suspect alt involves 3</t>
         </is>
       </c>
     </row>
